--- a/data/trans_orig/P36BPD04_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD04_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta o zumos naturales en 2023</t>
+          <t>Población según la frecuencia de consumo de fruta o zumos naturales en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19374</t>
+          <t>18599</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40717</t>
+          <t>40126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22178</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39352</t>
+          <t>38983</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45971</t>
+          <t>46430</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74519</t>
+          <t>73357</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68951</t>
+          <t>71414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99545</t>
+          <t>100727</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96866</t>
+          <t>96474</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125928</t>
+          <t>126878</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173268</t>
+          <t>174025</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215925</t>
+          <t>217098</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>281066</t>
+          <t>283453</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>323084</t>
+          <t>324486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>440055</t>
+          <t>438212</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>482291</t>
+          <t>481695</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>737179</t>
+          <t>733854</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>795712</t>
+          <t>791895</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,41%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84361</t>
+          <t>83068</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115927</t>
+          <t>115992</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136978</t>
+          <t>135438</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172482</t>
+          <t>171827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>227198</t>
+          <t>227235</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>276839</t>
+          <t>275403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96669</t>
+          <t>101381</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>177759</t>
+          <t>183416</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>113078</t>
+          <t>114747</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>847110</t>
+          <t>786021</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>251435</t>
+          <t>254915</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1098980</t>
+          <t>1075412</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>291709</t>
+          <t>265292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>474701</t>
+          <t>471901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>232318</t>
+          <t>235772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>369732</t>
+          <t>372115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>591573</t>
+          <t>572520</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>824457</t>
+          <t>810138</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1220522</t>
+          <t>1216119</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1631766</t>
+          <t>1642654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>855551</t>
+          <t>900811</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1330378</t>
+          <t>1332754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2206260</t>
+          <t>2197196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2810450</t>
+          <t>2799945</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,86%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>270358</t>
+          <t>265071</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>454994</t>
+          <t>451228</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>314368</t>
+          <t>323435</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>520659</t>
+          <t>512128</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665889</t>
+          <t>652400</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>924128</t>
+          <t>925936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17438</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64327</t>
+          <t>63281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30616</t>
+          <t>29672</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54413</t>
+          <t>53871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>53550</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99363</t>
+          <t>104386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97244</t>
+          <t>98545</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>140726</t>
+          <t>141737</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85034</t>
+          <t>84912</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>119782</t>
+          <t>118789</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>192939</t>
+          <t>191308</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>248454</t>
+          <t>247028</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>338452</t>
+          <t>336150</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>394943</t>
+          <t>393087</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>355714</t>
+          <t>355081</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>400164</t>
+          <t>400558</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>708969</t>
+          <t>709296</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>777559</t>
+          <t>781896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,82%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112791</t>
+          <t>113935</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156270</t>
+          <t>156491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123274</t>
+          <t>122317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161519</t>
+          <t>159741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248631</t>
+          <t>247815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>302076</t>
+          <t>302310</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>153944</t>
+          <t>156602</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>244466</t>
+          <t>245989</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>180568</t>
+          <t>183384</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1105345</t>
+          <t>1017759</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>373420</t>
+          <t>378960</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1274171</t>
+          <t>1357987</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>466283</t>
+          <t>477330</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>678493</t>
+          <t>679579</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>427090</t>
+          <t>424226</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>582158</t>
+          <t>582206</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1001843</t>
+          <t>976509</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1241345</t>
+          <t>1232278</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1886588</t>
+          <t>1886607</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2342108</t>
+          <t>2327614</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1600542</t>
+          <t>1636760</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2181335</t>
+          <t>2169707</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3677029</t>
+          <t>3728496</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4350995</t>
+          <t>4360500</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,4%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>494960</t>
+          <t>482482</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>694519</t>
+          <t>690555</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>597326</t>
+          <t>594072</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>802753</t>
+          <t>804695</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1174326</t>
+          <t>1158098</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1470988</t>
+          <t>1455719</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD04_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD04_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28559</t>
+          <t>30404</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18599</t>
+          <t>20650</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40126</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29375</t>
+          <t>32327</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>23382</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38983</t>
+          <t>41862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57934</t>
+          <t>62731</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46430</t>
+          <t>49594</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73357</t>
+          <t>78190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83763</t>
+          <t>93723</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71414</t>
+          <t>77629</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100727</t>
+          <t>112222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>111124</t>
+          <t>120881</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96474</t>
+          <t>105781</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126878</t>
+          <t>136054</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>194886</t>
+          <t>214604</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174025</t>
+          <t>190419</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217098</t>
+          <t>237574</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>303581</t>
+          <t>334112</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>283453</t>
+          <t>309836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>324486</t>
+          <t>357459</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>461334</t>
+          <t>504653</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>438212</t>
+          <t>483261</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>481695</t>
+          <t>526536</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>764914</t>
+          <t>838765</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>733854</t>
+          <t>806484</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>791895</t>
+          <t>869435</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>99036</t>
+          <t>120290</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83068</t>
+          <t>100603</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115992</t>
+          <t>142579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>152188</t>
+          <t>162662</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>135438</t>
+          <t>144912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>171827</t>
+          <t>181981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>251224</t>
+          <t>282951</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>227235</t>
+          <t>256483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>275403</t>
+          <t>309581</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>754021</t>
+          <t>820523</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>754021</t>
+          <t>820523</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>754021</t>
+          <t>820523</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1268959</t>
+          <t>1399052</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1268959</t>
+          <t>1399052</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1268959</t>
+          <t>1399052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>144349</t>
+          <t>152554</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>101381</t>
+          <t>124632</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>183416</t>
+          <t>182447</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>315614</t>
+          <t>124245</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>114747</t>
+          <t>105134</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>786021</t>
+          <t>146787</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>459963</t>
+          <t>276798</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>254915</t>
+          <t>243778</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1075412</t>
+          <t>313780</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>406808</t>
+          <t>418953</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>265292</t>
+          <t>377587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>471901</t>
+          <t>468675</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>317043</t>
+          <t>344442</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>235772</t>
+          <t>314963</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>372115</t>
+          <t>378721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>723851</t>
+          <t>763394</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>572520</t>
+          <t>710811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>810138</t>
+          <t>819388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1350944</t>
+          <t>1210009</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1216119</t>
+          <t>1152465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1642654</t>
+          <t>1262871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1180583</t>
+          <t>1256583</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>900811</t>
+          <t>1215627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1332754</t>
+          <t>1300917</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2531527</t>
+          <t>2466593</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2197196</t>
+          <t>2394488</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2799945</t>
+          <t>2533100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>57,57%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>387196</t>
+          <t>447969</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>265071</t>
+          <t>405047</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>451228</t>
+          <t>496269</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>423472</t>
+          <t>444995</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>323435</t>
+          <t>412250</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>512128</t>
+          <t>484743</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>810667</t>
+          <t>892964</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>652400</t>
+          <t>840608</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>925936</t>
+          <t>953851</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2236711</t>
+          <t>2170264</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2236711</t>
+          <t>2170264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2236711</t>
+          <t>2170264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4526009</t>
+          <t>4399749</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4526009</t>
+          <t>4399749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4526009</t>
+          <t>4399749</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>30843</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63281</t>
+          <t>40042</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40266</t>
+          <t>43772</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29672</t>
+          <t>32517</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53871</t>
+          <t>57877</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>71109</t>
+          <t>70388</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53550</t>
+          <t>54235</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104386</t>
+          <t>88120</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>116683</t>
+          <t>123634</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98545</t>
+          <t>102536</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>141737</t>
+          <t>147907</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>101167</t>
+          <t>107137</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>84912</t>
+          <t>91302</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118789</t>
+          <t>125059</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>217850</t>
+          <t>230771</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>191308</t>
+          <t>202974</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>247028</t>
+          <t>262927</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>365338</t>
+          <t>407750</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>336150</t>
+          <t>378468</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>393087</t>
+          <t>436471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>378457</t>
+          <t>422613</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>355081</t>
+          <t>397751</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>400558</t>
+          <t>445435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>743794</t>
+          <t>830364</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>709296</t>
+          <t>796956</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>781896</t>
+          <t>869279</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>60,1%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>133760</t>
+          <t>153586</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113935</t>
+          <t>128757</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156491</t>
+          <t>178420</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>140573</t>
+          <t>161355</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122317</t>
+          <t>142132</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159741</t>
+          <t>181878</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>274333</t>
+          <t>314941</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247815</t>
+          <t>285122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>302310</t>
+          <t>348587</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>203751</t>
+          <t>209574</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>156602</t>
+          <t>179189</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>245989</t>
+          <t>245858</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>385255</t>
+          <t>200344</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>183384</t>
+          <t>175547</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1017759</t>
+          <t>226505</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>589006</t>
+          <t>409917</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>378960</t>
+          <t>368889</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1357987</t>
+          <t>453729</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>607253</t>
+          <t>636311</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>477330</t>
+          <t>580972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>679579</t>
+          <t>687846</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>529334</t>
+          <t>572459</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>424226</t>
+          <t>533482</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>582206</t>
+          <t>614082</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1136587</t>
+          <t>1208770</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>976509</t>
+          <t>1145709</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1232278</t>
+          <t>1270533</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2019863</t>
+          <t>1951872</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1886607</t>
+          <t>1887426</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2327614</t>
+          <t>2019818</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2020373</t>
+          <t>2183850</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1636760</t>
+          <t>2125866</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2169707</t>
+          <t>2242730</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>4040236</t>
+          <t>4135722</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3728496</t>
+          <t>4051554</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4360500</t>
+          <t>4224445</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>58,31%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>619992</t>
+          <t>721845</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>482482</t>
+          <t>671050</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>690555</t>
+          <t>780262</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>716233</t>
+          <t>769011</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>594072</t>
+          <t>724055</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>804695</t>
+          <t>813709</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1336225</t>
+          <t>1490857</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1158098</t>
+          <t>1416350</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1455719</t>
+          <t>1560034</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3651195</t>
+          <t>3725664</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3651195</t>
+          <t>3725664</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3651195</t>
+          <t>3725664</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7102054</t>
+          <t>7245265</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7102054</t>
+          <t>7245265</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7102054</t>
+          <t>7245265</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
